--- a/office-agent/evals/xlsx/tasks/02-monthly-summary/inputs/transactions.xlsx
+++ b/office-agent/evals/xlsx/tasks/02-monthly-summary/inputs/transactions.xlsx
@@ -29,8 +29,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
